--- a/public/Items-Polish Items.xlsx
+++ b/public/Items-Polish Items.xlsx
@@ -489,7 +489,7 @@
   </sheetData>
   <dataValidations>
     <dataValidation type="list" allowBlank="true" showInputMessage="undefined" prompt="undefined" promptTitle="undefined" showErrorMessage="undefined" error="undefined" errorTitle="undefined" operator="undefined" sqref="A2:A1000">
-      <formula1>"Flap Disc,Non Woven Pad,Felt buff Pad,Cutting Blade,Welding Rod,Polish,Grinding Wheel,Core Bit"</formula1>
+      <formula1>"Flap Disc,Non Woven Pad,Felt buff Pad,Cutting Blade,Welding Rod,Polish,Grinding Wheel,Core Bit,Spray"</formula1>
       <formula2/>
     </dataValidation>
   </dataValidations>
